--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -514,7 +514,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>136.5</v>
+        <v>147.26</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>129.74</v>
+        <v>141.23</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>124.18</v>
+        <v>133.8</v>
       </c>
     </row>
     <row r="5">
@@ -565,7 +565,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>122</v>
+        <v>131.83</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>121.46</v>
+        <v>130.45</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>117.12</v>
+        <v>126.62</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>115.04</v>
+        <v>123.93</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>112.08</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="10">
@@ -650,7 +650,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>107.98</v>
+        <v>116.62</v>
       </c>
     </row>
     <row r="11">
@@ -667,7 +667,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>97.88</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>92.14</v>
+        <v>99.78</v>
       </c>
     </row>
     <row r="13">
@@ -701,7 +701,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>58.29</v>
+        <v>60.93</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:29</t>
+    <t xml:space="preserve">2026-10-05 16:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
